--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:03:47+00:00</t>
+    <t>2023-10-16T13:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:05:21+00:00</t>
+    <t>2023-10-16T13:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-bp</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-bp</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:49:57+00:00</t>
+    <t>2023-10-23T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1113,7 +1113,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
 </t>
   </si>
   <si>
@@ -1205,7 +1205,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|http://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person)
 </t>
   </si>
   <si>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T09:15:45+00:00</t>
+    <t>2023-10-23T11:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:28:06+00:00</t>
+    <t>2023-11-06T10:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T09:05:25+00:00</t>
+    <t>2023-11-08T15:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1539,7 +1539,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>http://interopsante.org/fhir/ValueSet/fr-core-bp-measurement-method</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-bp-measurement-method</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2740,7 +2740,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.33203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.76171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="26.1796875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T15:11:22+00:00</t>
+    <t>2023-11-21T10:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -443,7 +443,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -463,7 +463,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -1806,7 +1806,7 @@
     <t>Used when reporting vital signs panel components.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T10:12:39+00:00</t>
+    <t>2023-12-04T10:06:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T10:06:25+00:00</t>
+    <t>2023-12-04T12:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:30:51+00:00</t>
+    <t>2023-12-04T12:32:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:19:21+00:00</t>
+    <t>2023-12-11T10:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:51:09+00:00</t>
+    <t>2023-12-11T13:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:13:22+00:00</t>
+    <t>2023-12-19T10:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>81</v>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>81</v>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>81</v>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:49:53+00:00</t>
+    <t>2023-12-22T08:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T08:30:59+00:00</t>
+    <t>2024-01-19T16:14:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:14:08+00:00</t>
+    <t>2024-01-22T11:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:15+00:00</t>
+    <t>2024-01-22T11:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:58+00:00</t>
+    <t>2024-01-29T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:14:55+00:00</t>
+    <t>2024-01-29T10:26:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:26:27+00:00</t>
+    <t>2024-02-05T10:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T10:12:17+00:00</t>
+    <t>2024-02-05T11:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1545,7 +1545,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-bp-measurement-method</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-bp-measurement-method</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2754,7 +2754,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.76171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.4609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="26.1796875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T11:48:42+00:00</t>
+    <t>2024-02-12T13:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T13:27:08+00:00</t>
+    <t>2024-02-12T14:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:02:40+00:00</t>
+    <t>2024-02-26T11:03:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:03:57+00:00</t>
+    <t>2024-03-04T10:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T10:55:37+00:00</t>
+    <t>2024-03-11T09:42:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T09:42:54+00:00</t>
+    <t>2024-03-11T10:34:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T10:34:02+00:00</t>
+    <t>2024-03-20T14:49:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/ig/main/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T14:49:36+00:00</t>
+    <t>2024-03-21T08:11:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
